--- a/buckman/validation/2024/expected_outputs/Table_3_expected.xlsx
+++ b/buckman/validation/2024/expected_outputs/Table_3_expected.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bradwolaver\projects\rg\santafe\buckman\validation\2024\expected_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9BFA33-C54D-41C1-9804-A8F3EFCE6897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BF9497D-9881-40D4-B53C-9A4822A89D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="1815" windowWidth="23820" windowHeight="10125" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="1425" windowWidth="16590" windowHeight="16575" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 3 - Pojoaque-Nambe Tesuqu" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Rio Pojoaque-Rio Nambe</t>
   </si>
@@ -43,6 +43,30 @@
     <t>Total
 Impact</t>
   </si>
+  <si>
+    <t>42.778** (42.781)</t>
+  </si>
+  <si>
+    <t>57.182** (57.185)</t>
+  </si>
+  <si>
+    <t>44.297** (44.306)</t>
+  </si>
+  <si>
+    <t>57.759** (57.768)</t>
+  </si>
+  <si>
+    <t>11.294** (11.295)</t>
+  </si>
+  <si>
+    <t>33.567** (33.568)</t>
+  </si>
+  <si>
+    <t>11.967** (11.968)</t>
+  </si>
+  <si>
+    <t>33.680* (33.711)</t>
+  </si>
 </sst>
 </file>
 
@@ -51,7 +75,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -73,13 +97,26 @@
       <sz val="11"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -116,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -134,6 +171,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,10 +483,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="4" width="19.140625" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="7" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" customHeight="1">
@@ -879,20 +922,20 @@
       <c r="B20" s="3">
         <v>14.404</v>
       </c>
-      <c r="C20" s="3">
-        <v>42.777999999999999</v>
-      </c>
-      <c r="D20" s="4">
-        <v>57.182000000000002</v>
+      <c r="C20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>7</v>
       </c>
       <c r="E20" s="3">
         <v>22.273</v>
       </c>
-      <c r="F20" s="3">
-        <v>11.294</v>
-      </c>
-      <c r="G20" s="4">
-        <v>33.567</v>
+      <c r="F20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -902,20 +945,20 @@
       <c r="B21" s="3">
         <v>13.462</v>
       </c>
-      <c r="C21" s="3">
-        <v>44.296999999999997</v>
-      </c>
-      <c r="D21" s="4">
-        <v>57.759</v>
+      <c r="C21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E21" s="3">
         <v>21.742999999999999</v>
       </c>
-      <c r="F21" s="3">
-        <v>11.967000000000001</v>
-      </c>
-      <c r="G21" s="4">
-        <v>33.68</v>
+      <c r="F21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7">
